--- a/RedditDataFormatted.xlsx
+++ b/RedditDataFormatted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sena Dela Cruz\Documents\_My Made Projects\SeniorProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sena Dela Cruz\Documents\_My Made Projects\Actual Senior Project\Senior-Project-F23\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABDE27B3-3CC1-4428-89C2-DD3CF8346C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419E787C-C98E-4EFF-8F68-58DD55385F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17805" yWindow="0" windowWidth="19665" windowHeight="21600"/>
+    <workbookView xWindow="53085" yWindow="660" windowWidth="20010" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RedditDataFormatted" sheetId="1" r:id="rId1"/>
@@ -367,7 +367,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1201,9 +1201,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">

--- a/RedditDataFormatted.xlsx
+++ b/RedditDataFormatted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sena Dela Cruz\Documents\_My Made Projects\Actual Senior Project\Senior-Project-F23\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419E787C-C98E-4EFF-8F68-58DD55385F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DDB364-9D20-4542-807D-57EEDB6DC85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53085" yWindow="660" windowWidth="20010" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="975" yWindow="0" windowWidth="18045" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RedditDataFormatted" sheetId="1" r:id="rId1"/>
@@ -845,8 +845,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1206,19 +1207,23 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
